--- a/Fase 2/Evidencias Proyecto/Evidencias de documentación/1.6 Informe TEC/Horas hombre en relación a Tareas.xlsx
+++ b/Fase 2/Evidencias Proyecto/Evidencias de documentación/1.6 Informe TEC/Horas hombre en relación a Tareas.xlsx
@@ -73,7 +73,7 @@
     <t>TH-1.3</t>
   </si>
   <si>
-    <t>Maquetado del UI para el formulario de registro usando React/Angular y la debida conexión con el backend</t>
+    <t>Maquetado del UI para el formulario de registro usando React + Ionic y la debida conexión con el backend</t>
   </si>
   <si>
     <t>Alonso Gonzalez</t>
@@ -347,7 +347,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -388,6 +388,9 @@
     </xf>
     <xf borderId="4" fillId="0" fontId="6" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf borderId="4" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="4" fillId="3" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
@@ -739,7 +742,7 @@
       <c r="A12" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="B12" s="11" t="s">
+      <c r="B12" s="15" t="s">
         <v>20</v>
       </c>
       <c r="C12" s="11">
@@ -778,7 +781,7 @@
       </c>
     </row>
     <row r="14" ht="62.25" customHeight="1">
-      <c r="A14" s="15" t="s">
+      <c r="A14" s="16" t="s">
         <v>24</v>
       </c>
       <c r="B14" s="11" t="s">
@@ -1261,16 +1264,16 @@
       </c>
     </row>
     <row r="38">
-      <c r="B38" s="16" t="s">
+      <c r="B38" s="17" t="s">
         <v>70</v>
       </c>
-      <c r="C38" s="17" t="s">
+      <c r="C38" s="18" t="s">
         <v>71</v>
       </c>
-      <c r="E38" s="16" t="s">
+      <c r="E38" s="17" t="s">
         <v>72</v>
       </c>
-      <c r="F38" s="17" t="s">
+      <c r="F38" s="18" t="s">
         <v>73</v>
       </c>
     </row>
